--- a/Assets/Resources/DataFiles/CharData/ExcelFile/FighterStatData.xlsx
+++ b/Assets/Resources/DataFiles/CharData/ExcelFile/FighterStatData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m\Documents\GitHub\Project2\Assets\Resources\DataFiles\ExcelFile\Class\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m\Documents\GitHub\Project2\Assets\Resources\DataFiles\CharData\ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7276A9C1-1AC9-4D04-AA23-37DC4E2E38D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA36F16D-71D7-40D1-BB78-C09465C6A6EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A8CC0692-9D11-440E-B5CC-1903C5375D4B}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="16">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -89,6 +89,14 @@
   </si>
   <si>
     <t>basePen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>baseSkillRange</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -159,14 +167,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
@@ -502,510 +507,537 @@
     <col min="9" max="9" width="13" customWidth="1"/>
     <col min="10" max="10" width="10.59765625" customWidth="1"/>
     <col min="11" max="11" width="13.3984375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A1" s="2" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>8</v>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" t="s">
         <v>13</v>
       </c>
+      <c r="M2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A3" s="2">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
         <v>10</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <v>12</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <v>5</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <v>5</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <v>5</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="2">
         <v>10</v>
       </c>
-      <c r="H3" s="3">
-        <v>1</v>
-      </c>
-      <c r="I3" s="3">
-        <v>1</v>
-      </c>
-      <c r="J3" s="3">
-        <v>1</v>
-      </c>
-      <c r="K3" s="3">
-        <v>1</v>
-      </c>
-      <c r="L3" s="3">
-        <v>1</v>
-      </c>
-      <c r="M3" s="1"/>
+      <c r="H3" s="2">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1</v>
+      </c>
+      <c r="K3" s="2">
+        <v>1</v>
+      </c>
+      <c r="L3" s="2">
+        <v>1</v>
+      </c>
+      <c r="M3" s="2">
+        <v>1</v>
+      </c>
       <c r="N3" s="1"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A4" s="2">
+      <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>15</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <v>14</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <v>7</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <v>7</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <v>6</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
         <v>11</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="2">
         <v>1.3</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="2">
         <v>1.2</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K4" s="2">
         <v>1.2</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="2">
         <v>2</v>
       </c>
-      <c r="M4" s="1"/>
+      <c r="M4" s="2">
+        <v>1</v>
+      </c>
       <c r="N4" s="1"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A5" s="2">
+      <c r="A5">
         <v>3</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>20</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>16</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>10</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <v>9</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <v>7</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <v>12</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="2">
         <v>1.5</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="2">
         <v>1.2</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="2">
         <v>1.4</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5" s="2">
         <v>1.4</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="2">
         <v>3</v>
       </c>
-      <c r="M5" s="1"/>
+      <c r="M5" s="2">
+        <v>1</v>
+      </c>
       <c r="N5" s="1"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A6" s="2">
+      <c r="A6">
         <v>4</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>25</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <v>18</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <v>13</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <v>11</v>
       </c>
-      <c r="F6" s="3">
-        <v>8</v>
-      </c>
-      <c r="G6" s="3">
+      <c r="F6" s="2">
+        <v>8</v>
+      </c>
+      <c r="G6" s="2">
         <v>13</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="2">
         <v>1.7</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="2">
         <v>1.3</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="2">
         <v>1.6</v>
       </c>
-      <c r="K6" s="3">
+      <c r="K6" s="2">
         <v>1.6</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="2">
         <v>4</v>
       </c>
-      <c r="M6" s="1"/>
+      <c r="M6" s="2">
+        <v>1</v>
+      </c>
       <c r="N6" s="1"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A7" s="2">
+      <c r="A7">
         <v>5</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <v>30</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="2">
         <v>20</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <v>16</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2">
         <v>13</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="2">
         <v>9</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="2">
         <v>14</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="2">
         <v>2</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="2">
         <v>1.4</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="2">
         <v>1.8</v>
       </c>
-      <c r="K7" s="3">
+      <c r="K7" s="2">
         <v>1.8</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L7" s="2">
         <v>5</v>
       </c>
-      <c r="M7" s="1"/>
+      <c r="M7" s="2">
+        <v>1</v>
+      </c>
       <c r="N7" s="1"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A8" s="2">
+      <c r="A8">
         <v>6</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <v>35</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="2">
         <v>22</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="2">
         <v>19</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="2">
         <v>15</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="2">
         <v>10</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="2">
         <v>15</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="2">
         <v>2.2000000000000002</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="2">
         <v>1.5</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="2">
         <v>2</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="2">
         <v>2</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="2">
         <v>6</v>
       </c>
-      <c r="M8" s="1"/>
+      <c r="M8" s="2">
+        <v>1</v>
+      </c>
       <c r="N8" s="1"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A9" s="2">
+      <c r="A9">
         <v>7</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="2">
         <v>40</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="2">
         <v>24</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="2">
         <v>22</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="2">
         <v>17</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="2">
         <v>11</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="2">
         <v>16</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="2">
         <v>2.5</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="2">
         <v>1.6</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="2">
         <v>2.2000000000000002</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="2">
         <v>2.2000000000000002</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="2">
         <v>7</v>
       </c>
-      <c r="M9" s="1"/>
+      <c r="M9" s="2">
+        <v>1</v>
+      </c>
       <c r="N9" s="1"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A10" s="2">
-        <v>8</v>
-      </c>
-      <c r="B10" s="3">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2">
         <v>45</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="2">
         <v>26</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="2">
         <v>25</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="2">
         <v>19</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="2">
         <v>12</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="2">
         <v>17</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="2">
         <v>2.7</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="2">
         <v>1.7</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J10" s="2">
         <v>2.4</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="2">
         <v>2.4</v>
       </c>
-      <c r="L10" s="3">
-        <v>8</v>
-      </c>
-      <c r="M10" s="1"/>
+      <c r="L10" s="2">
+        <v>8</v>
+      </c>
+      <c r="M10" s="2">
+        <v>1</v>
+      </c>
       <c r="N10" s="1"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A11" s="2">
+      <c r="A11">
         <v>9</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="2">
         <v>50</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="2">
         <v>28</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="2">
         <v>28</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="2">
         <v>21</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="2">
         <v>13</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="2">
         <v>18</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="2">
         <v>3</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="2">
         <v>1.8</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J11" s="2">
         <v>2.6</v>
       </c>
-      <c r="K11" s="3">
+      <c r="K11" s="2">
         <v>2.6</v>
       </c>
-      <c r="L11" s="3">
+      <c r="L11" s="2">
         <v>9</v>
       </c>
-      <c r="M11" s="1"/>
+      <c r="M11" s="2">
+        <v>1</v>
+      </c>
       <c r="N11" s="1"/>
     </row>
     <row r="12" spans="1:14" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="4">
+      <c r="A12" s="3">
         <v>10</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="4">
         <v>55</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="4">
         <v>30</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="4">
         <v>31</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="4">
         <v>23</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="4">
         <v>14</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="4">
         <v>19</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="4">
         <v>3.2</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I12" s="4">
         <v>1.9</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J12" s="4">
         <v>2.8</v>
       </c>
-      <c r="K12" s="5">
+      <c r="K12" s="4">
         <v>2.8</v>
       </c>
-      <c r="L12" s="5">
+      <c r="L12" s="4">
         <v>10</v>
       </c>
-      <c r="M12" s="1"/>
+      <c r="M12" s="4">
+        <v>1</v>
+      </c>
       <c r="N12" s="1"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G13" s="3"/>
+      <c r="G13" s="2"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G14" s="3"/>
+      <c r="G14" s="2"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G15" s="3"/>
+      <c r="G15" s="2"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G16" s="3"/>
+      <c r="G16" s="2"/>
     </row>
     <row r="17" spans="7:7" x14ac:dyDescent="0.4">
-      <c r="G17" s="3"/>
+      <c r="G17" s="2"/>
     </row>
     <row r="18" spans="7:7" x14ac:dyDescent="0.4">
-      <c r="G18" s="3"/>
+      <c r="G18" s="2"/>
     </row>
     <row r="19" spans="7:7" x14ac:dyDescent="0.4">
-      <c r="G19" s="3"/>
+      <c r="G19" s="2"/>
     </row>
     <row r="20" spans="7:7" x14ac:dyDescent="0.4">
-      <c r="G20" s="3"/>
+      <c r="G20" s="2"/>
     </row>
     <row r="21" spans="7:7" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="G21" s="5"/>
+      <c r="G21" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Assets/Resources/DataFiles/CharData/ExcelFile/FighterStatData.xlsx
+++ b/Assets/Resources/DataFiles/CharData/ExcelFile/FighterStatData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m\Documents\GitHub\Project2\Assets\Resources\DataFiles\CharData\ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA36F16D-71D7-40D1-BB78-C09465C6A6EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{645928D6-5C5F-40DB-8F32-979979D15E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A8CC0692-9D11-440E-B5CC-1903C5375D4B}"/>
   </bookViews>
@@ -615,7 +615,7 @@
         <v>10</v>
       </c>
       <c r="H3" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I3" s="2">
         <v>1</v>
@@ -657,7 +657,7 @@
         <v>11</v>
       </c>
       <c r="H4" s="2">
-        <v>1.3</v>
+        <v>5.2</v>
       </c>
       <c r="I4" s="2">
         <v>1.1000000000000001</v>
@@ -699,7 +699,7 @@
         <v>12</v>
       </c>
       <c r="H5" s="2">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="I5" s="2">
         <v>1.2</v>
@@ -741,7 +741,7 @@
         <v>13</v>
       </c>
       <c r="H6" s="2">
-        <v>1.7</v>
+        <v>5.7</v>
       </c>
       <c r="I6" s="2">
         <v>1.3</v>
@@ -783,7 +783,7 @@
         <v>14</v>
       </c>
       <c r="H7" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I7" s="2">
         <v>1.4</v>
@@ -825,7 +825,7 @@
         <v>15</v>
       </c>
       <c r="H8" s="2">
-        <v>2.2000000000000002</v>
+        <v>6.2</v>
       </c>
       <c r="I8" s="2">
         <v>1.5</v>
@@ -867,7 +867,7 @@
         <v>16</v>
       </c>
       <c r="H9" s="2">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="I9" s="2">
         <v>1.6</v>
@@ -909,7 +909,7 @@
         <v>17</v>
       </c>
       <c r="H10" s="2">
-        <v>2.7</v>
+        <v>6.7</v>
       </c>
       <c r="I10" s="2">
         <v>1.7</v>
@@ -951,7 +951,7 @@
         <v>18</v>
       </c>
       <c r="H11" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I11" s="2">
         <v>1.8</v>
@@ -992,8 +992,8 @@
       <c r="G12" s="4">
         <v>19</v>
       </c>
-      <c r="H12" s="4">
-        <v>3.2</v>
+      <c r="H12" s="2">
+        <v>7.2</v>
       </c>
       <c r="I12" s="4">
         <v>1.9</v>

--- a/Assets/Resources/DataFiles/CharData/ExcelFile/FighterStatData.xlsx
+++ b/Assets/Resources/DataFiles/CharData/ExcelFile/FighterStatData.xlsx
@@ -1,52 +1,114 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m\Documents\GitHub\Project2\Assets\Resources\DataFiles\CharData\ExcelFile\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C74BAD-41AC-433A-81E2-1AB80918347C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="17">
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t xml:space="preserve">float </t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>maxHP</t>
+  </si>
+  <si>
+    <t>maxMP</t>
+  </si>
+  <si>
+    <t>baseATK</t>
+  </si>
+  <si>
+    <t>baseDEF</t>
+  </si>
+  <si>
+    <t>baseCritRate</t>
+  </si>
+  <si>
+    <t>baseCritMult</t>
+  </si>
+  <si>
+    <t>baseMS</t>
+  </si>
+  <si>
+    <t>baseAS</t>
+  </si>
+  <si>
+    <t>baseCDR</t>
+  </si>
+  <si>
+    <t>baseMPRegen</t>
+  </si>
+  <si>
+    <t>basePen</t>
+  </si>
+  <si>
+    <t>baseSkillRange</t>
+  </si>
+  <si>
+    <t>expToNextLevel</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
+      <family val="2"/>
       <charset val="129"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="8"/>
       <name val="맑은 고딕"/>
+      <family val="2"/>
       <charset val="129"/>
-      <family val="2"/>
-      <sz val="8"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
+      <family val="2"/>
       <charset val="129"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -71,113 +133,45 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -477,1048 +471,990 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col width="11.59765625" bestFit="1" customWidth="1" style="5" min="6" max="6"/>
-    <col width="20" customWidth="1" style="5" min="7" max="7"/>
-    <col width="13.19921875" customWidth="1" style="5" min="8" max="8"/>
-    <col width="13" customWidth="1" style="5" min="9" max="9"/>
-    <col width="10.59765625" customWidth="1" style="5" min="10" max="10"/>
-    <col width="13.3984375" bestFit="1" customWidth="1" style="5" min="11" max="11"/>
-    <col width="13.69921875" bestFit="1" customWidth="1" style="5" min="13" max="13"/>
+    <col min="6" max="6" width="11.59765625" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20" style="5" customWidth="1"/>
+    <col min="8" max="8" width="13.19921875" style="5" customWidth="1"/>
+    <col min="9" max="9" width="13" style="5" customWidth="1"/>
+    <col min="10" max="10" width="10.59765625" style="5" customWidth="1"/>
+    <col min="11" max="11" width="13.3984375" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.69921875" style="5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="B1" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">float </t>
-        </is>
-      </c>
-      <c r="C1" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">float </t>
-        </is>
-      </c>
-      <c r="D1" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">float </t>
-        </is>
-      </c>
-      <c r="E1" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">float </t>
-        </is>
-      </c>
-      <c r="F1" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">float </t>
-        </is>
-      </c>
-      <c r="G1" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">float </t>
-        </is>
-      </c>
-      <c r="H1" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">float </t>
-        </is>
-      </c>
-      <c r="I1" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">float </t>
-        </is>
-      </c>
-      <c r="J1" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">float </t>
-        </is>
-      </c>
-      <c r="K1" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">float </t>
-        </is>
-      </c>
-      <c r="L1" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">float </t>
-        </is>
-      </c>
-      <c r="M1" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N1" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="0" t="inlineStr">
-        <is>
-          <t>level</t>
-        </is>
-      </c>
-      <c r="B2" s="0" t="inlineStr">
-        <is>
-          <t>maxHP</t>
-        </is>
-      </c>
-      <c r="C2" s="0" t="inlineStr">
-        <is>
-          <t>maxMP</t>
-        </is>
-      </c>
-      <c r="D2" s="0" t="inlineStr">
-        <is>
-          <t>baseATK</t>
-        </is>
-      </c>
-      <c r="E2" s="0" t="inlineStr">
-        <is>
-          <t>baseDEF</t>
-        </is>
-      </c>
-      <c r="F2" s="0" t="inlineStr">
-        <is>
-          <t>baseCritRate</t>
-        </is>
-      </c>
-      <c r="G2" s="0" t="inlineStr">
-        <is>
-          <t>baseCritMult</t>
-        </is>
-      </c>
-      <c r="H2" s="0" t="inlineStr">
-        <is>
-          <t>baseMS</t>
-        </is>
-      </c>
-      <c r="I2" s="0" t="inlineStr">
-        <is>
-          <t>baseAS</t>
-        </is>
-      </c>
-      <c r="J2" s="0" t="inlineStr">
-        <is>
-          <t>baseCDR</t>
-        </is>
-      </c>
-      <c r="K2" s="0" t="inlineStr">
-        <is>
-          <t>baseMPRegen</t>
-        </is>
-      </c>
-      <c r="L2" s="0" t="inlineStr">
-        <is>
-          <t>basePen</t>
-        </is>
-      </c>
-      <c r="M2" s="0" t="inlineStr">
-        <is>
-          <t>baseSkillRange</t>
-        </is>
-      </c>
-      <c r="N2" s="0" t="inlineStr">
-        <is>
-          <t>expToNextLevel</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="6" t="n">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="I2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="K2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2">
+        <v>12</v>
+      </c>
+      <c r="D3" s="2">
         <v>5</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="2">
         <v>5</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="2">
         <v>5</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="G3" s="2">
         <v>10</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="H3" s="2">
         <v>5</v>
       </c>
-      <c r="I3" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" s="7" t="n">
+      <c r="I3" s="2">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1</v>
+      </c>
+      <c r="K3" s="2">
+        <v>1</v>
+      </c>
+      <c r="L3" s="2">
+        <v>1</v>
+      </c>
+      <c r="M3" s="2">
+        <v>1</v>
+      </c>
+      <c r="N3" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="0" t="n">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="2">
         <v>15</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C4" s="2">
         <v>14</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="2">
         <v>7</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="2">
         <v>7</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="2">
         <v>6</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="G4" s="2">
         <v>11</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="H4" s="2">
         <v>5.2</v>
       </c>
-      <c r="I4" s="6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J4" s="6" t="n">
+      <c r="I4" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J4" s="2">
         <v>1.2</v>
       </c>
-      <c r="K4" s="6" t="n">
+      <c r="K4" s="2">
         <v>1.2</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="L4" s="2">
         <v>2</v>
       </c>
-      <c r="M4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" s="7" t="n">
+      <c r="M4" s="2">
+        <v>1</v>
+      </c>
+      <c r="N4" s="1">
         <v>80</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="0" t="n">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A5">
         <v>3</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="2">
         <v>20</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="2">
         <v>16</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="2">
         <v>10</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="2">
         <v>9</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="2">
         <v>7</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="2">
         <v>12</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" s="2">
         <v>5.5</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I5" s="2">
         <v>1.2</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="J5" s="2">
         <v>1.4</v>
       </c>
-      <c r="K5" s="6" t="n">
+      <c r="K5" s="2">
         <v>1.4</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="L5" s="2">
         <v>3</v>
       </c>
-      <c r="M5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" s="7" t="n">
+      <c r="M5" s="2">
+        <v>1</v>
+      </c>
+      <c r="N5" s="1">
         <v>120</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="0" t="n">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A6">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="2">
         <v>25</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="2">
         <v>18</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="2">
         <v>13</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="2">
         <v>11</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="2">
         <v>8</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="2">
         <v>13</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" s="2">
         <v>5.7</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="2">
         <v>1.3</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="J6" s="2">
         <v>1.6</v>
       </c>
-      <c r="K6" s="6" t="n">
+      <c r="K6" s="2">
         <v>1.6</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="L6" s="2">
         <v>4</v>
       </c>
-      <c r="M6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" s="7" t="n">
+      <c r="M6" s="2">
+        <v>1</v>
+      </c>
+      <c r="N6" s="1">
         <v>170</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="0" t="n">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A7">
         <v>5</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="2">
         <v>30</v>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="2">
         <v>20</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="2">
         <v>16</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="2">
         <v>13</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="2">
         <v>9</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="2">
         <v>14</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="2">
         <v>6</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="I7" s="2">
         <v>1.4</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="J7" s="2">
         <v>1.8</v>
       </c>
-      <c r="K7" s="6" t="n">
+      <c r="K7" s="2">
         <v>1.8</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="L7" s="2">
         <v>5</v>
       </c>
-      <c r="M7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" s="7" t="n">
+      <c r="M7" s="2">
+        <v>1</v>
+      </c>
+      <c r="N7" s="1">
         <v>230</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="0" t="n">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A8">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="2">
         <v>35</v>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="2">
         <v>22</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="2">
         <v>19</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="2">
         <v>15</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="2">
         <v>10</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="G8" s="2">
         <v>15</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H8" s="2">
         <v>6.2</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="I8" s="2">
         <v>1.5</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="J8" s="2">
         <v>2</v>
       </c>
-      <c r="K8" s="6" t="n">
+      <c r="K8" s="2">
         <v>2</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="L8" s="2">
         <v>6</v>
       </c>
-      <c r="M8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" s="7" t="n">
+      <c r="M8" s="2">
+        <v>1</v>
+      </c>
+      <c r="N8" s="1">
         <v>300</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="0" t="n">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A9">
         <v>7</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="2">
         <v>40</v>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C9" s="2">
         <v>24</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="2">
         <v>22</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="2">
         <v>17</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="2">
         <v>11</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="G9" s="2">
         <v>16</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="H9" s="2">
         <v>6.5</v>
       </c>
-      <c r="I9" s="6" t="n">
+      <c r="I9" s="2">
         <v>1.6</v>
       </c>
-      <c r="J9" s="6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="K9" s="6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="L9" s="6" t="n">
+      <c r="J9" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="K9" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="L9" s="2">
         <v>7</v>
       </c>
-      <c r="M9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" s="7" t="n">
+      <c r="M9" s="2">
+        <v>1</v>
+      </c>
+      <c r="N9" s="1">
         <v>380</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="0" t="n">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A10">
         <v>8</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="2">
         <v>45</v>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C10" s="2">
         <v>26</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="2">
         <v>25</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="2">
         <v>19</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="2">
         <v>12</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="G10" s="2">
         <v>17</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H10" s="2">
         <v>6.7</v>
       </c>
-      <c r="I10" s="6" t="n">
+      <c r="I10" s="2">
         <v>1.7</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J10" s="2">
         <v>2.4</v>
       </c>
-      <c r="K10" s="6" t="n">
+      <c r="K10" s="2">
         <v>2.4</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="L10" s="2">
         <v>8</v>
       </c>
-      <c r="M10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" s="7" t="n">
+      <c r="M10" s="2">
+        <v>1</v>
+      </c>
+      <c r="N10" s="1">
         <v>470</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="0" t="n">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A11">
         <v>9</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="2">
         <v>50</v>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C11" s="2">
         <v>28</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="2">
         <v>28</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="2">
         <v>21</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="2">
         <v>13</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="G11" s="2">
         <v>18</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="2">
         <v>7</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="I11" s="2">
         <v>1.8</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" s="2">
         <v>2.6</v>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="K11" s="2">
         <v>2.6</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="L11" s="2">
         <v>9</v>
       </c>
-      <c r="M11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" s="7" t="n">
+      <c r="M11" s="2">
+        <v>1</v>
+      </c>
+      <c r="N11" s="1">
         <v>570</v>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1" s="5" thickBot="1">
-      <c r="A12" s="3" t="n">
+    <row r="12" spans="1:14" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="3">
         <v>10</v>
       </c>
-      <c r="B12" s="8" t="n">
+      <c r="B12" s="4">
         <v>55</v>
       </c>
-      <c r="C12" s="8" t="n">
+      <c r="C12" s="4">
         <v>30</v>
       </c>
-      <c r="D12" s="8" t="n">
+      <c r="D12" s="4">
         <v>31</v>
       </c>
-      <c r="E12" s="8" t="n">
+      <c r="E12" s="4">
         <v>23</v>
       </c>
-      <c r="F12" s="8" t="n">
+      <c r="F12" s="4">
         <v>14</v>
       </c>
-      <c r="G12" s="8" t="n">
+      <c r="G12" s="4">
         <v>19</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="H12" s="2">
         <v>7.2</v>
       </c>
-      <c r="I12" s="8" t="n">
+      <c r="I12" s="4">
         <v>1.9</v>
       </c>
-      <c r="J12" s="8" t="n">
+      <c r="J12" s="4">
         <v>2.8</v>
       </c>
-      <c r="K12" s="8" t="n">
+      <c r="K12" s="4">
         <v>2.8</v>
       </c>
-      <c r="L12" s="8" t="n">
+      <c r="L12" s="4">
         <v>10</v>
       </c>
-      <c r="M12" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" s="7" t="n">
+      <c r="M12" s="4">
+        <v>1</v>
+      </c>
+      <c r="N12" s="1">
         <v>680</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A13">
         <v>11</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>60</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>32</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>34</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>25</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>15</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="G13" s="2">
         <v>20</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>7.5</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>2</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13">
         <v>3</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13">
         <v>3</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13">
         <v>11</v>
       </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
         <v>800</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A14">
         <v>12</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>65</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>34</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>37</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>27</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>16</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="G14" s="2">
         <v>21</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>7.7</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14">
         <v>2.1</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14">
         <v>3.2</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14">
         <v>3.2</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14">
         <v>12</v>
       </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
         <v>930</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A15">
         <v>13</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>70</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>36</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>40</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>29</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>17</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="G15" s="2">
         <v>22</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15">
         <v>8</v>
       </c>
-      <c r="I15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J15" t="n">
+      <c r="I15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="J15">
         <v>3.4</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15">
         <v>3.4</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15">
         <v>13</v>
       </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="n">
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
         <v>1070</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A16">
         <v>14</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>75</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>38</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>43</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>31</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>18</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="G16" s="2">
         <v>23</v>
       </c>
-      <c r="H16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J16" t="n">
+      <c r="H16">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="I16">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="J16">
         <v>3.6</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16">
         <v>3.6</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16">
         <v>14</v>
       </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
         <v>1220</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A17">
         <v>15</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>80</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>40</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>46</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>33</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>19</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="G17" s="2">
         <v>24</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17">
         <v>8.5</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17">
         <v>2.4</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17">
         <v>3.8</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17">
         <v>3.8</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17">
         <v>15</v>
       </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
         <v>1380</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A18">
         <v>16</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>85</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>42</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>49</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>35</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18">
         <v>20</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="G18" s="2">
         <v>25</v>
       </c>
-      <c r="H18" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="I18" t="n">
+      <c r="H18">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="I18">
         <v>2.5</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18">
         <v>4</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K18">
         <v>4</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L18">
         <v>16</v>
       </c>
-      <c r="M18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" t="n">
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
         <v>1550</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A19">
         <v>17</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>90</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>44</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>52</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>37</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19">
         <v>21</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="G19" s="2">
         <v>26</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19">
         <v>9</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19">
         <v>2.6</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19">
         <v>4.2</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K19">
         <v>4.2</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L19">
         <v>17</v>
       </c>
-      <c r="M19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" t="n">
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="N19">
         <v>1730</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A20">
         <v>18</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>95</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>46</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>55</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>39</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20">
         <v>22</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="G20" s="2">
         <v>27</v>
       </c>
-      <c r="H20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="I20" t="n">
+      <c r="H20">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="I20">
         <v>2.7</v>
       </c>
-      <c r="J20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L20" t="n">
+      <c r="J20">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="K20">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="L20">
         <v>18</v>
       </c>
-      <c r="M20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" t="n">
+      <c r="M20">
+        <v>1</v>
+      </c>
+      <c r="N20">
         <v>1920</v>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1" s="5" thickBot="1">
-      <c r="A21" t="n">
+    <row r="21" spans="1:14" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21">
         <v>19</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>100</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>48</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>58</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21">
         <v>41</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21">
         <v>23</v>
       </c>
-      <c r="G21" s="8" t="n">
+      <c r="G21" s="4">
         <v>28</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21">
         <v>9.5</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21">
         <v>2.8</v>
       </c>
-      <c r="J21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L21" t="n">
+      <c r="J21">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="K21">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="L21">
         <v>19</v>
       </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
+      <c r="M21">
+        <v>1</v>
+      </c>
+      <c r="N21">
         <v>2120</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A22">
         <v>20</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>105</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>50</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>61</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>43</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22">
         <v>24</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22">
         <v>29</v>
       </c>
-      <c r="H22" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="I22" t="n">
+      <c r="H22">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="I22">
         <v>2.9</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J22">
         <v>4.8</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K22">
         <v>4.8</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L22">
         <v>20</v>
       </c>
-      <c r="M22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" t="n">
+      <c r="M22">
+        <v>1</v>
+      </c>
+      <c r="N22">
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Assets/Resources/DataFiles/CharData/ExcelFile/FighterStatData.xlsx
+++ b/Assets/Resources/DataFiles/CharData/ExcelFile/FighterStatData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m\Documents\GitHub\Project2\Assets\Resources\DataFiles\CharData\ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C74BAD-41AC-433A-81E2-1AB80918347C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96E0D0DD-C16F-422F-A33F-F386E6A3DCA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5772" yWindow="372" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -581,7 +581,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="2">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="D3" s="2">
         <v>5</v>
@@ -625,7 +625,7 @@
         <v>15</v>
       </c>
       <c r="C4" s="2">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="D4" s="2">
         <v>7</v>
@@ -669,7 +669,7 @@
         <v>20</v>
       </c>
       <c r="C5" s="2">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="D5" s="2">
         <v>10</v>
@@ -713,7 +713,7 @@
         <v>25</v>
       </c>
       <c r="C6" s="2">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="D6" s="2">
         <v>13</v>
@@ -757,7 +757,7 @@
         <v>30</v>
       </c>
       <c r="C7" s="2">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D7" s="2">
         <v>16</v>
@@ -801,7 +801,7 @@
         <v>35</v>
       </c>
       <c r="C8" s="2">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="D8" s="2">
         <v>19</v>
@@ -845,7 +845,7 @@
         <v>40</v>
       </c>
       <c r="C9" s="2">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="D9" s="2">
         <v>22</v>
@@ -889,7 +889,7 @@
         <v>45</v>
       </c>
       <c r="C10" s="2">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="D10" s="2">
         <v>25</v>
@@ -933,7 +933,7 @@
         <v>50</v>
       </c>
       <c r="C11" s="2">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="D11" s="2">
         <v>28</v>
@@ -976,8 +976,8 @@
       <c r="B12" s="4">
         <v>55</v>
       </c>
-      <c r="C12" s="4">
-        <v>30</v>
+      <c r="C12" s="2">
+        <v>70</v>
       </c>
       <c r="D12" s="4">
         <v>31</v>
@@ -1020,8 +1020,8 @@
       <c r="B13">
         <v>60</v>
       </c>
-      <c r="C13">
-        <v>32</v>
+      <c r="C13" s="2">
+        <v>75</v>
       </c>
       <c r="D13">
         <v>34</v>
@@ -1064,8 +1064,8 @@
       <c r="B14">
         <v>65</v>
       </c>
-      <c r="C14">
-        <v>34</v>
+      <c r="C14" s="2">
+        <v>75</v>
       </c>
       <c r="D14">
         <v>37</v>
@@ -1108,8 +1108,8 @@
       <c r="B15">
         <v>70</v>
       </c>
-      <c r="C15">
-        <v>36</v>
+      <c r="C15" s="2">
+        <v>80</v>
       </c>
       <c r="D15">
         <v>40</v>
@@ -1152,8 +1152,8 @@
       <c r="B16">
         <v>75</v>
       </c>
-      <c r="C16">
-        <v>38</v>
+      <c r="C16" s="2">
+        <v>80</v>
       </c>
       <c r="D16">
         <v>43</v>
@@ -1196,8 +1196,8 @@
       <c r="B17">
         <v>80</v>
       </c>
-      <c r="C17">
-        <v>40</v>
+      <c r="C17" s="2">
+        <v>85</v>
       </c>
       <c r="D17">
         <v>46</v>
@@ -1240,8 +1240,8 @@
       <c r="B18">
         <v>85</v>
       </c>
-      <c r="C18">
-        <v>42</v>
+      <c r="C18" s="2">
+        <v>85</v>
       </c>
       <c r="D18">
         <v>49</v>
@@ -1284,8 +1284,8 @@
       <c r="B19">
         <v>90</v>
       </c>
-      <c r="C19">
-        <v>44</v>
+      <c r="C19" s="2">
+        <v>90</v>
       </c>
       <c r="D19">
         <v>52</v>
@@ -1328,8 +1328,8 @@
       <c r="B20">
         <v>95</v>
       </c>
-      <c r="C20">
-        <v>46</v>
+      <c r="C20" s="2">
+        <v>90</v>
       </c>
       <c r="D20">
         <v>55</v>
@@ -1372,8 +1372,8 @@
       <c r="B21">
         <v>100</v>
       </c>
-      <c r="C21">
-        <v>48</v>
+      <c r="C21" s="2">
+        <v>95</v>
       </c>
       <c r="D21">
         <v>58</v>
@@ -1416,8 +1416,8 @@
       <c r="B22">
         <v>105</v>
       </c>
-      <c r="C22">
-        <v>50</v>
+      <c r="C22" s="2">
+        <v>100</v>
       </c>
       <c r="D22">
         <v>61</v>

--- a/Assets/Resources/DataFiles/CharData/ExcelFile/FighterStatData.xlsx
+++ b/Assets/Resources/DataFiles/CharData/ExcelFile/FighterStatData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m\Documents\GitHub\Project2\Assets\Resources\DataFiles\CharData\ExcelFile\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Project2\Assets\Resources\DataFiles\CharData\ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96E0D0DD-C16F-422F-A33F-F386E6A3DCA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B76E7AA0-B658-449E-A3A8-10D8F081F4CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5772" yWindow="372" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -77,11 +77,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+  <numFmts count="1">
+    <numFmt numFmtId="177" formatCode="0.0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -97,14 +96,6 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -114,7 +105,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -122,44 +113,22 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+  <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -473,19 +442,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N22"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="6" max="6" width="11.59765625" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20" style="5" customWidth="1"/>
-    <col min="8" max="8" width="13.19921875" style="5" customWidth="1"/>
-    <col min="9" max="9" width="13" style="5" customWidth="1"/>
-    <col min="10" max="10" width="10.59765625" style="5" customWidth="1"/>
-    <col min="11" max="11" width="13.3984375" style="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.69921875" style="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.25" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -529,7 +498,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -573,8 +542,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
         <v>1</v>
       </c>
       <c r="B3" s="2">
@@ -611,14 +580,14 @@
         <v>1</v>
       </c>
       <c r="M3" s="2">
-        <v>1</v>
-      </c>
-      <c r="N3" s="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="2">
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A4">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
         <v>2</v>
       </c>
       <c r="B4" s="2">
@@ -655,14 +624,14 @@
         <v>2</v>
       </c>
       <c r="M4" s="2">
-        <v>1</v>
-      </c>
-      <c r="N4" s="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A5">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
         <v>3</v>
       </c>
       <c r="B5" s="2">
@@ -699,14 +668,14 @@
         <v>3</v>
       </c>
       <c r="M5" s="2">
-        <v>1</v>
-      </c>
-      <c r="N5" s="1">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2">
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A6">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
         <v>4</v>
       </c>
       <c r="B6" s="2">
@@ -743,14 +712,14 @@
         <v>4</v>
       </c>
       <c r="M6" s="2">
-        <v>1</v>
-      </c>
-      <c r="N6" s="1">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2">
         <v>170</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A7">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
         <v>5</v>
       </c>
       <c r="B7" s="2">
@@ -787,14 +756,14 @@
         <v>5</v>
       </c>
       <c r="M7" s="2">
-        <v>1</v>
-      </c>
-      <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2">
         <v>230</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A8">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
         <v>6</v>
       </c>
       <c r="B8" s="2">
@@ -831,14 +800,14 @@
         <v>6</v>
       </c>
       <c r="M8" s="2">
-        <v>1</v>
-      </c>
-      <c r="N8" s="1">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2">
         <v>300</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A9">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
         <v>7</v>
       </c>
       <c r="B9" s="2">
@@ -875,14 +844,14 @@
         <v>7</v>
       </c>
       <c r="M9" s="2">
-        <v>1</v>
-      </c>
-      <c r="N9" s="1">
+        <v>0</v>
+      </c>
+      <c r="N9" s="2">
         <v>380</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A10">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
         <v>8</v>
       </c>
       <c r="B10" s="2">
@@ -919,14 +888,14 @@
         <v>8</v>
       </c>
       <c r="M10" s="2">
-        <v>1</v>
-      </c>
-      <c r="N10" s="1">
+        <v>0</v>
+      </c>
+      <c r="N10" s="2">
         <v>470</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A11">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
         <v>9</v>
       </c>
       <c r="B11" s="2">
@@ -963,493 +932,493 @@
         <v>9</v>
       </c>
       <c r="M11" s="2">
-        <v>1</v>
-      </c>
-      <c r="N11" s="1">
+        <v>0</v>
+      </c>
+      <c r="N11" s="2">
         <v>570</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="3">
+    <row r="12" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
         <v>10</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="2">
         <v>55</v>
       </c>
       <c r="C12" s="2">
         <v>70</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="2">
         <v>31</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="2">
         <v>23</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="2">
         <v>14</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="2">
         <v>19</v>
       </c>
       <c r="H12" s="2">
         <v>7.2</v>
       </c>
-      <c r="I12" s="4">
+      <c r="I12" s="2">
         <v>1.9</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J12" s="2">
         <v>2.8</v>
       </c>
-      <c r="K12" s="4">
+      <c r="K12" s="2">
         <v>2.8</v>
       </c>
-      <c r="L12" s="4">
+      <c r="L12" s="2">
         <v>10</v>
       </c>
-      <c r="M12" s="4">
-        <v>1</v>
-      </c>
-      <c r="N12" s="1">
+      <c r="M12" s="2">
+        <v>0</v>
+      </c>
+      <c r="N12" s="2">
         <v>680</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A13">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
         <v>11</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="2">
         <v>60</v>
       </c>
       <c r="C13" s="2">
         <v>75</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="2">
         <v>34</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="2">
         <v>25</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="2">
         <v>15</v>
       </c>
       <c r="G13" s="2">
         <v>20</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="2">
         <v>7.5</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="2">
         <v>2</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="2">
         <v>3</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="2">
         <v>3</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="2">
         <v>11</v>
       </c>
-      <c r="M13">
-        <v>1</v>
-      </c>
-      <c r="N13">
+      <c r="M13" s="2">
+        <v>0</v>
+      </c>
+      <c r="N13" s="2">
         <v>800</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
         <v>12</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="2">
         <v>65</v>
       </c>
       <c r="C14" s="2">
         <v>75</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="2">
         <v>37</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="2">
         <v>27</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="2">
         <v>16</v>
       </c>
       <c r="G14" s="2">
         <v>21</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="2">
         <v>7.7</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="2">
         <v>2.1</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="2">
         <v>3.2</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="2">
         <v>3.2</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="2">
         <v>12</v>
       </c>
-      <c r="M14">
-        <v>1</v>
-      </c>
-      <c r="N14">
+      <c r="M14" s="2">
+        <v>0</v>
+      </c>
+      <c r="N14" s="2">
         <v>930</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A15">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
         <v>13</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="2">
         <v>70</v>
       </c>
       <c r="C15" s="2">
         <v>80</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="2">
         <v>40</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="2">
         <v>29</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="2">
         <v>17</v>
       </c>
       <c r="G15" s="2">
         <v>22</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="2">
         <v>8</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="2">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="2">
         <v>3.4</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="2">
         <v>3.4</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="2">
         <v>13</v>
       </c>
-      <c r="M15">
-        <v>1</v>
-      </c>
-      <c r="N15">
+      <c r="M15" s="2">
+        <v>0</v>
+      </c>
+      <c r="N15" s="2">
         <v>1070</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A16">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
         <v>14</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="2">
         <v>75</v>
       </c>
       <c r="C16" s="2">
         <v>80</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="2">
         <v>43</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="2">
         <v>31</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="2">
         <v>18</v>
       </c>
       <c r="G16" s="2">
         <v>23</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="2">
         <v>8.1999999999999993</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="2">
         <v>3.6</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="2">
         <v>3.6</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="2">
         <v>14</v>
       </c>
-      <c r="M16">
-        <v>1</v>
-      </c>
-      <c r="N16">
+      <c r="M16" s="2">
+        <v>0</v>
+      </c>
+      <c r="N16" s="2">
         <v>1220</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A17">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
         <v>15</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="2">
         <v>80</v>
       </c>
       <c r="C17" s="2">
         <v>85</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="2">
         <v>46</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="2">
         <v>33</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="2">
         <v>19</v>
       </c>
       <c r="G17" s="2">
         <v>24</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="2">
         <v>8.5</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="2">
         <v>2.4</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="2">
         <v>3.8</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="2">
         <v>3.8</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="2">
         <v>15</v>
       </c>
-      <c r="M17">
-        <v>1</v>
-      </c>
-      <c r="N17">
+      <c r="M17" s="2">
+        <v>0</v>
+      </c>
+      <c r="N17" s="2">
         <v>1380</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A18">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
         <v>16</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="2">
         <v>85</v>
       </c>
       <c r="C18" s="2">
         <v>85</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="2">
         <v>49</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="2">
         <v>35</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="2">
         <v>20</v>
       </c>
       <c r="G18" s="2">
         <v>25</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="2">
         <v>8.6999999999999993</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="2">
         <v>2.5</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="2">
         <v>4</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="2">
         <v>4</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="2">
         <v>16</v>
       </c>
-      <c r="M18">
-        <v>1</v>
-      </c>
-      <c r="N18">
+      <c r="M18" s="2">
+        <v>0</v>
+      </c>
+      <c r="N18" s="2">
         <v>1550</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A19">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
         <v>17</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="2">
         <v>90</v>
       </c>
       <c r="C19" s="2">
         <v>90</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="2">
         <v>52</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="2">
         <v>37</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="2">
         <v>21</v>
       </c>
       <c r="G19" s="2">
         <v>26</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="2">
         <v>9</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="2">
         <v>2.6</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="2">
         <v>4.2</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="2">
         <v>4.2</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="2">
         <v>17</v>
       </c>
-      <c r="M19">
-        <v>1</v>
-      </c>
-      <c r="N19">
+      <c r="M19" s="2">
+        <v>0</v>
+      </c>
+      <c r="N19" s="2">
         <v>1730</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A20">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
         <v>18</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="2">
         <v>95</v>
       </c>
       <c r="C20" s="2">
         <v>90</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="2">
         <v>55</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="2">
         <v>39</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="2">
         <v>22</v>
       </c>
       <c r="G20" s="2">
         <v>27</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="2">
         <v>9.1999999999999993</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="2">
         <v>2.7</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="2">
         <v>4.4000000000000004</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="2">
         <v>4.4000000000000004</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="2">
         <v>18</v>
       </c>
-      <c r="M20">
-        <v>1</v>
-      </c>
-      <c r="N20">
+      <c r="M20" s="2">
+        <v>0</v>
+      </c>
+      <c r="N20" s="2">
         <v>1920</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21">
+    <row r="21" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
         <v>19</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="2">
         <v>100</v>
       </c>
       <c r="C21" s="2">
         <v>95</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="2">
         <v>58</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="2">
         <v>41</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="2">
         <v>23</v>
       </c>
-      <c r="G21" s="4">
+      <c r="G21" s="2">
         <v>28</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="2">
         <v>9.5</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="2">
         <v>2.8</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="2">
         <v>4.5999999999999996</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="2">
         <v>4.5999999999999996</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="2">
         <v>19</v>
       </c>
-      <c r="M21">
-        <v>1</v>
-      </c>
-      <c r="N21">
+      <c r="M21" s="2">
+        <v>0</v>
+      </c>
+      <c r="N21" s="2">
         <v>2120</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A22">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
         <v>20</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="2">
         <v>105</v>
       </c>
       <c r="C22" s="2">
         <v>100</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="2">
         <v>61</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="2">
         <v>43</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="2">
         <v>24</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="2">
         <v>29</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="2">
         <v>9.6999999999999993</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="2">
         <v>2.9</v>
       </c>
-      <c r="J22">
+      <c r="J22" s="2">
         <v>4.8</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="2">
         <v>4.8</v>
       </c>
-      <c r="L22">
+      <c r="L22" s="2">
         <v>20</v>
       </c>
-      <c r="M22">
-        <v>1</v>
-      </c>
-      <c r="N22">
+      <c r="M22" s="2">
+        <v>0</v>
+      </c>
+      <c r="N22" s="2">
         <v>0</v>
       </c>
     </row>
